--- a/data/trans_orig/IP3110_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15392</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>20,39%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>39470</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>29810</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>49982</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>15,95%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>12,05%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>20,2%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>39470</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>30172</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>51079</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43947</t>
+          <t>44162</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61080</t>
+          <t>60826</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46591</t>
+          <t>44773</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76370</t>
+          <t>77092</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97661</t>
+          <t>97256</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131682</t>
+          <t>130866</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28963</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>23919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62913</t>
+          <t>62183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44888</t>
+          <t>44530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86210</t>
+          <t>85130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>19342</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33150</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>17003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18470</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33994</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27074</t>
+          <t>28020</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49010</t>
+          <t>50034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>50357</t>
+          <t>50443</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76196</t>
+          <t>75265</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69459</t>
+          <t>68213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94374</t>
+          <t>93689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84025</t>
+          <t>84641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113494</t>
+          <t>114171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160647</t>
+          <t>159899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200323</t>
+          <t>199377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>30682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50815</t>
+          <t>49741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>38541</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62373</t>
+          <t>64003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74523</t>
+          <t>76077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106118</t>
+          <t>105845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>16703</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>30923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29935</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>56505</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50417</t>
+          <t>50742</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>80831</t>
+          <t>82063</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20057</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28164</t>
+          <t>29440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39598</t>
+          <t>38693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>23602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42365</t>
+          <t>44696</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43847</t>
+          <t>42902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73929</t>
+          <t>74136</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96745</t>
+          <t>94316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69332</t>
+          <t>70094</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>97715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123261</t>
+          <t>122216</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>182453</t>
+          <t>182464</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>31541</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>106660</t>
+          <t>112312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>33149</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>56907</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73467</t>
+          <t>73919</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167839</t>
+          <t>169737</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>24787</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>17341</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37582</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40818</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56229</t>
+          <t>56091</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30383</t>
+          <t>30696</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49113</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70660</t>
+          <t>70788</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98960</t>
+          <t>98833</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47641</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>68066</t>
+          <t>68345</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>51402</t>
+          <t>52732</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74166</t>
+          <t>75118</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>105558</t>
+          <t>106459</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>136696</t>
+          <t>135822</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38639</t>
+          <t>39108</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42630</t>
+          <t>41865</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65272</t>
+          <t>66032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>26314</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27792</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>47855</t>
+          <t>48670</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23177</t>
+          <t>23406</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51837</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>34591</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59097</t>
+          <t>59053</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70858</t>
+          <t>71348</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>101199</t>
+          <t>103231</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>100453</t>
+          <t>100603</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>139570</t>
+          <t>139248</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>107056</t>
+          <t>107952</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>146086</t>
+          <t>147416</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>218872</t>
+          <t>219720</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>270935</t>
+          <t>273279</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>227127</t>
+          <t>231260</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>292417</t>
+          <t>293671</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>280156</t>
+          <t>278181</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>333335</t>
+          <t>336364</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>532236</t>
+          <t>531070</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>613258</t>
+          <t>619216</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>113773</t>
+          <t>112716</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>226612</t>
+          <t>210872</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>138523</t>
+          <t>136519</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>192477</t>
+          <t>191386</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>265888</t>
+          <t>263680</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>368978</t>
+          <t>373524</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>78814</t>
+          <t>77311</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>69896</t>
+          <t>68306</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>105842</t>
+          <t>105084</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>129866</t>
+          <t>128320</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>174260</t>
+          <t>175909</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>44336</t>
+          <t>44390</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3110_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4356</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8962</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3869</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7233</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17298</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10958</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26457</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21414</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15318</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28996</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>39470</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29810</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49982</t>
+          <t>51213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53512</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38948</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63714</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>43,74%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>31,84%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>52,08%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>52307</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>44162</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>60826</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>46,58%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>39,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>54,16%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62683</t>
+          <t>54127</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44773</t>
+          <t>46417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77092</t>
+          <t>64539</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>114990</t>
+          <t>107639</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97256</t>
+          <t>92265</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>130866</t>
+          <t>121702</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>50,9%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33610</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23163</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>54738</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18,93%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21756</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15731</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28731</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62183</t>
+          <t>30588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58255</t>
+          <t>56613</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44530</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85130</t>
+          <t>78658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12737</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20747</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12214</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7226</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18205</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>19117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>25605</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>17739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>820</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>122334</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>122334</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>122334</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>112304</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>112304</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>112304</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>116759</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>116759</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>116759</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>135104</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>135104</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>135104</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>349</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>247408</t>
+          <t>239093</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>247408</t>
+          <t>239093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247408</t>
+          <t>239093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12197</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19679</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10798</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6154</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17003</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>25512</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34761</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>31319</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23270</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41644</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>25136</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18024</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33837</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,32%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28020</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50034</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>61821</t>
+          <t>56641</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>50443</t>
+          <t>45057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>75265</t>
+          <t>69058</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>92756</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>79045</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>106238</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>80524</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>68213</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>93689</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>43,6%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>98871</t>
+          <t>73625</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84641</t>
+          <t>62886</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114171</t>
+          <t>84586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>179395</t>
+          <t>166380</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159899</t>
+          <t>149369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199377</t>
+          <t>184628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47964</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37511</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>60129</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>26,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>39151</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30682</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>49741</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,2%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50381</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64003</t>
+          <t>51018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>89532</t>
+          <t>88193</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76077</t>
+          <t>73208</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105845</t>
+          <t>104764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>40186</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17,38%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13,01%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>23366</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>16703</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56505</t>
+          <t>32382</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>63436</t>
+          <t>64476</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50742</t>
+          <t>51468</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>82063</t>
+          <t>80418</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6819</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3074</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12880</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5734</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2690</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10222</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>184709</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>184709</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>184709</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>178979</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>178979</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>178979</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>247520</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>247520</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>247520</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>592</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>432229</t>
+          <t>410220</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>432229</t>
+          <t>410220</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>432229</t>
+          <t>410220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6336</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10595</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>12881</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6944</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20821</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,09%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29440</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>28740</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>21444</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>38509</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17,26%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>23,13%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>27468</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>15221</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>38693</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>14,63%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>20,61%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32022</t>
+          <t>25531</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23602</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44696</t>
+          <t>34942</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>59490</t>
+          <t>54271</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42902</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74136</t>
+          <t>67672</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>77186</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>65085</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>91085</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>46,35%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>39,09%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>54,7%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>77157</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>42197</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>94316</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>41,1%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>50,24%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>83108</t>
+          <t>72818</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70094</t>
+          <t>62227</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97715</t>
+          <t>84300</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>160265</t>
+          <t>150004</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122216</t>
+          <t>132308</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>182464</t>
+          <t>166931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>38248</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>28883</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49203</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>22,97%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>17,35%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,55%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>57006</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>31541</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>112312</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>30,37%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>59,83%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44102</t>
+          <t>30308</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>40680</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>101108</t>
+          <t>68556</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73919</t>
+          <t>55637</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>169737</t>
+          <t>84210</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14777</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8920</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>22936</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>9961</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4818</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>16498</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24787</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>25274</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36589</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5215</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8366</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>187728</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>187728</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>187728</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>154601</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>154601</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>154601</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>183089</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>183089</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>183089</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>442</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>370817</t>
+          <t>321123</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>370817</t>
+          <t>321123</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>370817</t>
+          <t>321123</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>15062</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9367</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>22187</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>12825</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>8199</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>18889</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17807</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26195</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>27292</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>20232</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>36742</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>6,13%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>30632</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>22950</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>42451</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>37384</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>29017</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>47964</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>22,5%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>17,46%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>28,87%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>45980</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>35751</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>56091</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>27,95%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>34,09%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>43586</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30696</t>
+          <t>34751</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50098</t>
+          <t>55000</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>85065</t>
+          <t>80970</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70788</t>
+          <t>68534</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98833</t>
+          <t>94730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>59455</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>48939</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>70538</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>35,78%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>42,45%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>57858</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>47528</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>68345</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>28,89%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>41,54%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>62947</t>
+          <t>59188</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52732</t>
+          <t>48880</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>75118</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>120805</t>
+          <t>118643</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>106459</t>
+          <t>105550</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>135822</t>
+          <t>135816</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>27172</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>19767</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>34928</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>21,02%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>23894</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>17394</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>32345</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>24091</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39108</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>53159</t>
+          <t>51263</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>41865</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>66032</t>
+          <t>62387</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>17226</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>11283</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>26020</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>18875</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>12326</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>26890</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>17790</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>27952</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>37065</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27720</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48670</t>
+          <t>50107</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9866</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>16898</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>5085</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2205</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>10244</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>163979</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>163979</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>163979</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>177309</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>177309</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>177309</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>467</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>37952</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>29225</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>50485</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>40373</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>30128</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>51529</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59053</t>
+          <t>47372</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>85406</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>71348</t>
+          <t>63309</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>103231</t>
+          <t>91287</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>114742</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>96436</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>133940</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>119999</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>100603</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>139248</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>116854</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>107952</t>
+          <t>102054</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>147416</t>
+          <t>133577</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>245846</t>
+          <t>231596</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>219720</t>
+          <t>208301</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>273279</t>
+          <t>256635</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>282909</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>257184</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>307842</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>41,22%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>385</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>267846</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>231260</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>293671</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>41,25%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>35,62%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>45,23%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>307608</t>
+          <t>259757</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>278181</t>
+          <t>239151</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>336364</t>
+          <t>280857</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>575455</t>
+          <t>542665</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>531070</t>
+          <t>510163</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>619216</t>
+          <t>575200</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,23%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>146995</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>126823</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>174502</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>18,48%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>25,43%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>141807</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>112716</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>210872</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>160247</t>
+          <t>117630</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>136519</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>191386</t>
+          <t>135713</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>302054</t>
+          <t>264625</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>263680</t>
+          <t>237938</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>373524</t>
+          <t>294409</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>84926</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>69817</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>105762</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>64416</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>50861</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>77311</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>67493</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>105084</t>
+          <t>81345</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>149624</t>
+          <t>152419</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>128320</t>
+          <t>130850</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>175909</t>
+          <t>175887</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>18739</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>27125</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>14818</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>9258</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>21321</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>25101</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>44390</t>
+          <t>45523</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>649260</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>649260</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>649260</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>614318</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>614318</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>614318</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>743022</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>743022</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>743022</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1850</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1392282</t>
+          <t>1300580</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1392282</t>
+          <t>1300580</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1392282</t>
+          <t>1300580</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
